--- a/branches/dev/StructureDefinition-selftest-model.xlsx
+++ b/branches/dev/StructureDefinition-selftest-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:21:01+00:00</t>
+    <t>2026-07-23T23:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-selftest-model.xlsx
+++ b/branches/dev/StructureDefinition-selftest-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:35:23+00:00</t>
+    <t>2026-07-23T23:49:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-selftest-model.xlsx
+++ b/branches/dev/StructureDefinition-selftest-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:49:03+00:00</t>
+    <t>2026-07-25T21:53:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-selftest-model.xlsx
+++ b/branches/dev/StructureDefinition-selftest-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T21:53:45+00:00</t>
+    <t>2026-07-25T22:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-selftest-model.xlsx
+++ b/branches/dev/StructureDefinition-selftest-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:03:00+00:00</t>
+    <t>2026-07-25T22:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-selftest-model.xlsx
+++ b/branches/dev/StructureDefinition-selftest-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:20:35+00:00</t>
+    <t>2026-07-25T22:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
